--- a/Team-Data/2007-08/12-30-2007-08.xlsx
+++ b/Team-Data/2007-08/12-30-2007-08.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>-0.5</v>
       </c>
       <c r="AD2" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE2" t="n">
         <v>14</v>
@@ -778,7 +845,7 @@
         <v>5</v>
       </c>
       <c r="AQ2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AR2" t="n">
         <v>11</v>
@@ -790,13 +857,13 @@
         <v>20</v>
       </c>
       <c r="AU2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV2" t="n">
         <v>19</v>
       </c>
       <c r="AW2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX2" t="n">
         <v>5</v>
@@ -805,7 +872,7 @@
         <v>19</v>
       </c>
       <c r="AZ2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BA2" t="n">
         <v>8</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -843,25 +910,25 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" t="n">
         <v>3</v>
       </c>
       <c r="G3" t="n">
-        <v>0.897</v>
+        <v>0.893</v>
       </c>
       <c r="H3" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>35.6</v>
+        <v>35.5</v>
       </c>
       <c r="J3" t="n">
-        <v>75.2</v>
+        <v>75.09999999999999</v>
       </c>
       <c r="K3" t="n">
         <v>0.473</v>
@@ -870,31 +937,31 @@
         <v>7.7</v>
       </c>
       <c r="M3" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.394</v>
+        <v>0.397</v>
       </c>
       <c r="O3" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="P3" t="n">
-        <v>28.2</v>
+        <v>27.9</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.77</v>
+        <v>0.772</v>
       </c>
       <c r="R3" t="n">
         <v>9.5</v>
       </c>
       <c r="S3" t="n">
-        <v>32.5</v>
+        <v>32.3</v>
       </c>
       <c r="T3" t="n">
-        <v>42</v>
+        <v>41.7</v>
       </c>
       <c r="U3" t="n">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="V3" t="n">
         <v>15.1</v>
@@ -909,19 +976,19 @@
         <v>4.7</v>
       </c>
       <c r="Z3" t="n">
-        <v>21.3</v>
+        <v>21</v>
       </c>
       <c r="AA3" t="n">
-        <v>23.1</v>
+        <v>22.9</v>
       </c>
       <c r="AB3" t="n">
-        <v>100.6</v>
+        <v>100.3</v>
       </c>
       <c r="AC3" t="n">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -936,7 +1003,7 @@
         <v>8</v>
       </c>
       <c r="AI3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AJ3" t="n">
         <v>30</v>
@@ -966,19 +1033,19 @@
         <v>29</v>
       </c>
       <c r="AS3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AT3" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="AU3" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AX3" t="n">
         <v>27</v>
@@ -987,13 +1054,13 @@
         <v>13</v>
       </c>
       <c r="AZ3" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BA3" t="n">
         <v>7</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>1</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1170,19 @@
         <v>-5.4</v>
       </c>
       <c r="AD4" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
         <v>24</v>
       </c>
       <c r="AH4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI4" t="n">
         <v>27</v>
@@ -1127,7 +1194,7 @@
         <v>22</v>
       </c>
       <c r="AL4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM4" t="n">
         <v>15</v>
@@ -1157,10 +1224,10 @@
         <v>24</v>
       </c>
       <c r="AV4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AW4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AX4" t="n">
         <v>18</v>
@@ -1169,13 +1236,13 @@
         <v>21</v>
       </c>
       <c r="AZ4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="BA4" t="n">
         <v>16</v>
       </c>
       <c r="BB4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BC4" t="n">
         <v>26</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -1207,16 +1274,16 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E5" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F5" t="n">
         <v>17</v>
       </c>
       <c r="G5" t="n">
-        <v>0.393</v>
+        <v>0.37</v>
       </c>
       <c r="H5" t="n">
         <v>48.2</v>
@@ -1225,40 +1292,40 @@
         <v>35</v>
       </c>
       <c r="J5" t="n">
-        <v>84.2</v>
+        <v>84.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0.416</v>
+        <v>0.413</v>
       </c>
       <c r="L5" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M5" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="N5" t="n">
-        <v>0.332</v>
+        <v>0.325</v>
       </c>
       <c r="O5" t="n">
-        <v>17</v>
+        <v>16.9</v>
       </c>
       <c r="P5" t="n">
-        <v>22.3</v>
+        <v>22.2</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.761</v>
+        <v>0.763</v>
       </c>
       <c r="R5" t="n">
-        <v>13.5</v>
+        <v>13.6</v>
       </c>
       <c r="S5" t="n">
-        <v>29.9</v>
+        <v>30</v>
       </c>
       <c r="T5" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U5" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="V5" t="n">
         <v>15.2</v>
@@ -1267,34 +1334,34 @@
         <v>7.6</v>
       </c>
       <c r="X5" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z5" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.8</v>
+        <v>21</v>
       </c>
       <c r="AB5" t="n">
-        <v>92.2</v>
+        <v>91.90000000000001</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4</v>
+        <v>-4.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="AE5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AH5" t="n">
         <v>18</v>
@@ -1303,19 +1370,19 @@
         <v>25</v>
       </c>
       <c r="AJ5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AK5" t="n">
         <v>30</v>
       </c>
       <c r="AL5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AM5" t="n">
         <v>24</v>
       </c>
       <c r="AN5" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="AO5" t="n">
         <v>24</v>
@@ -1324,13 +1391,13 @@
         <v>25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR5" t="n">
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AT5" t="n">
         <v>9</v>
@@ -1342,16 +1409,16 @@
         <v>15</v>
       </c>
       <c r="AW5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX5" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AY5" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AZ5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA5" t="n">
         <v>19</v>
@@ -1360,7 +1427,7 @@
         <v>30</v>
       </c>
       <c r="BC5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1540,7 @@
         <v>18</v>
       </c>
       <c r="AF6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AG6" t="n">
         <v>19</v>
@@ -1497,7 +1564,7 @@
         <v>13</v>
       </c>
       <c r="AN6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AO6" t="n">
         <v>19</v>
@@ -1527,7 +1594,7 @@
         <v>18</v>
       </c>
       <c r="AX6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AY6" t="n">
         <v>18</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -1652,13 +1719,13 @@
         <v>3</v>
       </c>
       <c r="AE7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AH7" t="n">
         <v>21</v>
@@ -1667,16 +1734,16 @@
         <v>17</v>
       </c>
       <c r="AJ7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL7" t="n">
         <v>17</v>
       </c>
       <c r="AM7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN7" t="n">
         <v>15</v>
@@ -1685,7 +1752,7 @@
         <v>2</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
         <v>1</v>
@@ -1697,7 +1764,7 @@
         <v>11</v>
       </c>
       <c r="AT7" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AU7" t="n">
         <v>19</v>
@@ -1721,10 +1788,10 @@
         <v>12</v>
       </c>
       <c r="BB7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BC7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -1753,97 +1820,97 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
         <v>18</v>
       </c>
       <c r="F8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6</v>
+        <v>0.621</v>
       </c>
       <c r="H8" t="n">
         <v>48.3</v>
       </c>
       <c r="I8" t="n">
-        <v>38.7</v>
+        <v>39</v>
       </c>
       <c r="J8" t="n">
         <v>84.8</v>
       </c>
       <c r="K8" t="n">
-        <v>0.456</v>
+        <v>0.46</v>
       </c>
       <c r="L8" t="n">
         <v>6.4</v>
       </c>
       <c r="M8" t="n">
-        <v>18.9</v>
+        <v>19</v>
       </c>
       <c r="N8" t="n">
-        <v>0.336</v>
+        <v>0.34</v>
       </c>
       <c r="O8" t="n">
-        <v>23.2</v>
+        <v>22.9</v>
       </c>
       <c r="P8" t="n">
-        <v>30.8</v>
+        <v>30.4</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.754</v>
+        <v>0.753</v>
       </c>
       <c r="R8" t="n">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="S8" t="n">
-        <v>33.3</v>
+        <v>33.2</v>
       </c>
       <c r="T8" t="n">
-        <v>44.9</v>
+        <v>44.5</v>
       </c>
       <c r="U8" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="V8" t="n">
-        <v>16.5</v>
+        <v>16.3</v>
       </c>
       <c r="W8" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="X8" t="n">
         <v>6.8</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="AA8" t="n">
-        <v>24.6</v>
+        <v>24.4</v>
       </c>
       <c r="AB8" t="n">
-        <v>106.9</v>
+        <v>107.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="AD8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE8" t="n">
         <v>9</v>
       </c>
       <c r="AF8" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AG8" t="n">
         <v>9</v>
       </c>
       <c r="AH8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI8" t="n">
         <v>4</v>
@@ -1852,16 +1919,16 @@
         <v>4</v>
       </c>
       <c r="AK8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL8" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AM8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AN8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1873,7 +1940,7 @@
         <v>16</v>
       </c>
       <c r="AR8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AS8" t="n">
         <v>4</v>
@@ -1885,19 +1952,19 @@
         <v>5</v>
       </c>
       <c r="AV8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW8" t="n">
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY8" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ8" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="BA8" t="n">
         <v>1</v>
@@ -1906,7 +1973,7 @@
         <v>3</v>
       </c>
       <c r="BC8" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>9.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE9" t="n">
         <v>2</v>
@@ -2028,13 +2095,13 @@
         <v>24</v>
       </c>
       <c r="AI9" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AJ9" t="n">
         <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AL9" t="n">
         <v>20</v>
@@ -2043,7 +2110,7 @@
         <v>23</v>
       </c>
       <c r="AN9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AO9" t="n">
         <v>11</v>
@@ -2052,13 +2119,13 @@
         <v>14</v>
       </c>
       <c r="AQ9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR9" t="n">
         <v>13</v>
       </c>
       <c r="AS9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT9" t="n">
         <v>24</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -2117,88 +2184,88 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F10" t="n">
         <v>13</v>
       </c>
       <c r="G10" t="n">
-        <v>0.581</v>
+        <v>0.5669999999999999</v>
       </c>
       <c r="H10" t="n">
         <v>48.3</v>
       </c>
       <c r="I10" t="n">
-        <v>40.1</v>
+        <v>40.2</v>
       </c>
       <c r="J10" t="n">
-        <v>89.59999999999999</v>
+        <v>89.7</v>
       </c>
       <c r="K10" t="n">
         <v>0.448</v>
       </c>
       <c r="L10" t="n">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
       <c r="M10" t="n">
-        <v>27.2</v>
+        <v>27.1</v>
       </c>
       <c r="N10" t="n">
-        <v>0.347</v>
+        <v>0.348</v>
       </c>
       <c r="O10" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="P10" t="n">
-        <v>25.2</v>
+        <v>25.1</v>
       </c>
       <c r="Q10" t="n">
         <v>0.74</v>
       </c>
       <c r="R10" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S10" t="n">
-        <v>30.1</v>
+        <v>30</v>
       </c>
       <c r="T10" t="n">
         <v>42.8</v>
       </c>
       <c r="U10" t="n">
-        <v>22.8</v>
+        <v>22.7</v>
       </c>
       <c r="V10" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W10" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X10" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y10" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Z10" t="n">
-        <v>23.4</v>
+        <v>23.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB10" t="n">
-        <v>108.4</v>
+        <v>108.5</v>
       </c>
       <c r="AC10" t="n">
-        <v>2</v>
+        <v>1.7</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AF10" t="n">
         <v>11</v>
@@ -2207,7 +2274,7 @@
         <v>11</v>
       </c>
       <c r="AH10" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2216,7 +2283,7 @@
         <v>1</v>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>1</v>
@@ -2225,10 +2292,10 @@
         <v>1</v>
       </c>
       <c r="AN10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AO10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AP10" t="n">
         <v>16</v>
@@ -2237,13 +2304,13 @@
         <v>21</v>
       </c>
       <c r="AR10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AS10" t="n">
         <v>17</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
         <v>8</v>
@@ -2255,22 +2322,22 @@
         <v>4</v>
       </c>
       <c r="AX10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AY10" t="n">
         <v>23</v>
       </c>
       <c r="AZ10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA10" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="BB10" t="n">
         <v>2</v>
       </c>
       <c r="BC10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD10" t="n">
         <v>10</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>1.4</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
         <v>14</v>
@@ -2389,7 +2456,7 @@
         <v>15</v>
       </c>
       <c r="AH11" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI11" t="n">
         <v>19</v>
@@ -2407,7 +2474,7 @@
         <v>8</v>
       </c>
       <c r="AN11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AO11" t="n">
         <v>27</v>
@@ -2419,7 +2486,7 @@
         <v>23</v>
       </c>
       <c r="AR11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AS11" t="n">
         <v>8</v>
@@ -2434,13 +2501,13 @@
         <v>10</v>
       </c>
       <c r="AW11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AX11" t="n">
         <v>4</v>
       </c>
       <c r="AY11" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ11" t="n">
         <v>9</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -2583,7 +2650,7 @@
         <v>19</v>
       </c>
       <c r="AL12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AM12" t="n">
         <v>4</v>
@@ -2592,10 +2659,10 @@
         <v>9</v>
       </c>
       <c r="AO12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AP12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AQ12" t="n">
         <v>17</v>
@@ -2604,13 +2671,13 @@
         <v>12</v>
       </c>
       <c r="AS12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT12" t="n">
         <v>5</v>
       </c>
       <c r="AU12" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV12" t="n">
         <v>18</v>
@@ -2634,7 +2701,7 @@
         <v>7</v>
       </c>
       <c r="BC12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-5.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AE13" t="n">
         <v>25</v>
@@ -2765,13 +2832,13 @@
         <v>29</v>
       </c>
       <c r="AL13" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM13" t="n">
         <v>25</v>
       </c>
       <c r="AN13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO13" t="n">
         <v>10</v>
@@ -2798,7 +2865,7 @@
         <v>11</v>
       </c>
       <c r="AW13" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AX13" t="n">
         <v>10</v>
@@ -2813,7 +2880,7 @@
         <v>15</v>
       </c>
       <c r="BB13" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC13" t="n">
         <v>27</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -2845,64 +2912,64 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E14" t="n">
         <v>19</v>
       </c>
       <c r="F14" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G14" t="n">
-        <v>0.633</v>
+        <v>0.655</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>38.5</v>
+        <v>38.9</v>
       </c>
       <c r="J14" t="n">
         <v>82.2</v>
       </c>
       <c r="K14" t="n">
-        <v>0.469</v>
+        <v>0.473</v>
       </c>
       <c r="L14" t="n">
         <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="N14" t="n">
-        <v>0.351</v>
+        <v>0.353</v>
       </c>
       <c r="O14" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="P14" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="Q14" t="n">
         <v>0.76</v>
       </c>
       <c r="R14" t="n">
-        <v>11.2</v>
+        <v>11.3</v>
       </c>
       <c r="S14" t="n">
-        <v>33.8</v>
+        <v>33.9</v>
       </c>
       <c r="T14" t="n">
-        <v>45</v>
+        <v>45.1</v>
       </c>
       <c r="U14" t="n">
-        <v>23.6</v>
+        <v>23.8</v>
       </c>
       <c r="V14" t="n">
         <v>15.7</v>
       </c>
       <c r="W14" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X14" t="n">
         <v>5</v>
@@ -2911,28 +2978,28 @@
         <v>4.6</v>
       </c>
       <c r="Z14" t="n">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.5</v>
+        <v>23.2</v>
       </c>
       <c r="AB14" t="n">
-        <v>106.5</v>
+        <v>107</v>
       </c>
       <c r="AC14" t="n">
-        <v>4.6</v>
+        <v>5.4</v>
       </c>
       <c r="AD14" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE14" t="n">
         <v>8</v>
       </c>
       <c r="AF14" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AH14" t="n">
         <v>24</v>
@@ -2965,16 +3032,16 @@
         <v>14</v>
       </c>
       <c r="AR14" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AS14" t="n">
         <v>2</v>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="n">
         <v>22</v>
@@ -2986,19 +3053,19 @@
         <v>14</v>
       </c>
       <c r="AY14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ14" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BA14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BB14" t="n">
         <v>4</v>
       </c>
       <c r="BC14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -3027,100 +3094,100 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E15" t="n">
         <v>8</v>
       </c>
       <c r="F15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G15" t="n">
-        <v>0.267</v>
+        <v>0.276</v>
       </c>
       <c r="H15" t="n">
         <v>48.3</v>
       </c>
       <c r="I15" t="n">
-        <v>36.8</v>
+        <v>36.9</v>
       </c>
       <c r="J15" t="n">
-        <v>80</v>
+        <v>80.2</v>
       </c>
       <c r="K15" t="n">
         <v>0.46</v>
       </c>
       <c r="L15" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M15" t="n">
-        <v>21.4</v>
+        <v>21.6</v>
       </c>
       <c r="N15" t="n">
-        <v>0.373</v>
+        <v>0.376</v>
       </c>
       <c r="O15" t="n">
-        <v>19</v>
+        <v>19.1</v>
       </c>
       <c r="P15" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.757</v>
+        <v>0.764</v>
       </c>
       <c r="R15" t="n">
-        <v>9.699999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="S15" t="n">
-        <v>31.3</v>
+        <v>31.6</v>
       </c>
       <c r="T15" t="n">
-        <v>41.1</v>
+        <v>41.4</v>
       </c>
       <c r="U15" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="V15" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W15" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="X15" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z15" t="n">
         <v>19.9</v>
       </c>
       <c r="AA15" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AB15" t="n">
-        <v>100.6</v>
+        <v>101</v>
       </c>
       <c r="AC15" t="n">
-        <v>-5</v>
+        <v>-4.3</v>
       </c>
       <c r="AD15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE15" t="n">
         <v>27</v>
       </c>
       <c r="AF15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AG15" t="n">
         <v>28</v>
       </c>
       <c r="AH15" t="n">
+        <v>11</v>
+      </c>
+      <c r="AI15" t="n">
         <v>12</v>
-      </c>
-      <c r="AI15" t="n">
-        <v>13</v>
       </c>
       <c r="AJ15" t="n">
         <v>18</v>
@@ -3129,7 +3196,7 @@
         <v>10</v>
       </c>
       <c r="AL15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM15" t="n">
         <v>5</v>
@@ -3138,28 +3205,28 @@
         <v>5</v>
       </c>
       <c r="AO15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AP15" t="n">
         <v>17</v>
       </c>
       <c r="AQ15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AS15" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AT15" t="n">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AU15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AW15" t="n">
         <v>30</v>
@@ -3168,19 +3235,19 @@
         <v>12</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AZ15" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BA15" t="n">
         <v>10</v>
       </c>
       <c r="BB15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BC15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3375,7 @@
         <v>28</v>
       </c>
       <c r="AK16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AL16" t="n">
         <v>27</v>
@@ -3317,13 +3384,13 @@
         <v>27</v>
       </c>
       <c r="AN16" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AP16" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ16" t="n">
         <v>29</v>
@@ -3350,16 +3417,16 @@
         <v>8</v>
       </c>
       <c r="AY16" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA16" t="n">
         <v>9</v>
       </c>
       <c r="BB16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC16" t="n">
         <v>25</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -3469,13 +3536,13 @@
         <v>-5</v>
       </c>
       <c r="AD17" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AE17" t="n">
         <v>21</v>
       </c>
       <c r="AF17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG17" t="n">
         <v>22</v>
@@ -3517,10 +3584,10 @@
         <v>27</v>
       </c>
       <c r="AT17" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AU17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AV17" t="n">
         <v>17</v>
@@ -3535,7 +3602,7 @@
         <v>22</v>
       </c>
       <c r="AZ17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BA17" t="n">
         <v>18</v>
@@ -3544,7 +3611,7 @@
         <v>18</v>
       </c>
       <c r="BC17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -3651,7 +3718,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3678,7 +3745,7 @@
         <v>18</v>
       </c>
       <c r="AM18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN18" t="n">
         <v>17</v>
@@ -3699,13 +3766,13 @@
         <v>25</v>
       </c>
       <c r="AT18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AU18" t="n">
         <v>28</v>
       </c>
       <c r="AV18" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AW18" t="n">
         <v>17</v>
@@ -3714,7 +3781,7 @@
         <v>25</v>
       </c>
       <c r="AY18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AZ18" t="n">
         <v>28</v>
@@ -3723,7 +3790,7 @@
         <v>29</v>
       </c>
       <c r="BB18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BC18" t="n">
         <v>30</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-5</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
@@ -3875,13 +3942,13 @@
         <v>22</v>
       </c>
       <c r="AR19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AU19" t="n">
         <v>7</v>
@@ -3893,7 +3960,7 @@
         <v>25</v>
       </c>
       <c r="AX19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AY19" t="n">
         <v>5</v>
@@ -3908,7 +3975,7 @@
         <v>29</v>
       </c>
       <c r="BC19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -4015,10 +4082,10 @@
         <v>4</v>
       </c>
       <c r="AD20" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AF20" t="n">
         <v>5</v>
@@ -4030,7 +4097,7 @@
         <v>4</v>
       </c>
       <c r="AI20" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ20" t="n">
         <v>9</v>
@@ -4066,7 +4133,7 @@
         <v>10</v>
       </c>
       <c r="AU20" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV20" t="n">
         <v>4</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -4119,58 +4186,58 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E21" t="n">
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G21" t="n">
-        <v>0.276</v>
+        <v>0.286</v>
       </c>
       <c r="H21" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I21" t="n">
-        <v>34.6</v>
+        <v>34.7</v>
       </c>
       <c r="J21" t="n">
-        <v>81</v>
+        <v>80.90000000000001</v>
       </c>
       <c r="K21" t="n">
-        <v>0.427</v>
+        <v>0.429</v>
       </c>
       <c r="L21" t="n">
         <v>5.5</v>
       </c>
       <c r="M21" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0.328</v>
+      </c>
+      <c r="O21" t="n">
+        <v>19.2</v>
+      </c>
+      <c r="P21" t="n">
+        <v>27.3</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0.703</v>
+      </c>
+      <c r="R21" t="n">
+        <v>13.1</v>
+      </c>
+      <c r="S21" t="n">
+        <v>29.1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>42.2</v>
+      </c>
+      <c r="U21" t="n">
         <v>16.8</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.326</v>
-      </c>
-      <c r="O21" t="n">
-        <v>19.1</v>
-      </c>
-      <c r="P21" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0.704</v>
-      </c>
-      <c r="R21" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="S21" t="n">
-        <v>29</v>
-      </c>
-      <c r="T21" t="n">
-        <v>42.4</v>
-      </c>
-      <c r="U21" t="n">
-        <v>16.7</v>
       </c>
       <c r="V21" t="n">
         <v>15.7</v>
@@ -4182,22 +4249,22 @@
         <v>2.4</v>
       </c>
       <c r="Y21" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="Z21" t="n">
-        <v>21.6</v>
+        <v>21.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>22</v>
+        <v>22.1</v>
       </c>
       <c r="AB21" t="n">
-        <v>93.8</v>
+        <v>94.2</v>
       </c>
       <c r="AC21" t="n">
-        <v>-8.199999999999999</v>
+        <v>-7.9</v>
       </c>
       <c r="AD21" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE21" t="n">
         <v>27</v>
@@ -4215,7 +4282,7 @@
         <v>26</v>
       </c>
       <c r="AJ21" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK21" t="n">
         <v>28</v>
@@ -4224,16 +4291,16 @@
         <v>21</v>
       </c>
       <c r="AM21" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AN21" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AO21" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AQ21" t="n">
         <v>28</v>
@@ -4263,13 +4330,13 @@
         <v>28</v>
       </c>
       <c r="AZ21" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BA21" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="BB21" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="BC21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -4382,10 +4449,10 @@
         <v>1</v>
       </c>
       <c r="AE22" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF22" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AG22" t="n">
         <v>6</v>
@@ -4409,7 +4476,7 @@
         <v>2</v>
       </c>
       <c r="AN22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO22" t="n">
         <v>8</v>
@@ -4421,7 +4488,7 @@
         <v>27</v>
       </c>
       <c r="AR22" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS22" t="n">
         <v>1</v>
@@ -4436,16 +4503,16 @@
         <v>16</v>
       </c>
       <c r="AW22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX22" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AY22" t="n">
         <v>9</v>
       </c>
       <c r="AZ22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BA22" t="n">
         <v>2</v>
@@ -4454,7 +4521,7 @@
         <v>6</v>
       </c>
       <c r="BC22" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD22" t="n">
         <v>10</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -4483,28 +4550,28 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E23" t="n">
         <v>13</v>
       </c>
       <c r="F23" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G23" t="n">
-        <v>0.433</v>
+        <v>0.448</v>
       </c>
       <c r="H23" t="n">
         <v>48.3</v>
       </c>
       <c r="I23" t="n">
-        <v>35.6</v>
+        <v>35.8</v>
       </c>
       <c r="J23" t="n">
-        <v>79.40000000000001</v>
+        <v>79.5</v>
       </c>
       <c r="K23" t="n">
-        <v>0.448</v>
+        <v>0.45</v>
       </c>
       <c r="L23" t="n">
         <v>4.2</v>
@@ -4513,34 +4580,34 @@
         <v>12.9</v>
       </c>
       <c r="N23" t="n">
-        <v>0.329</v>
+        <v>0.33</v>
       </c>
       <c r="O23" t="n">
-        <v>17.5</v>
+        <v>17.9</v>
       </c>
       <c r="P23" t="n">
-        <v>24.4</v>
+        <v>24.9</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.72</v>
+        <v>0.718</v>
       </c>
       <c r="R23" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S23" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T23" t="n">
         <v>42.2</v>
       </c>
       <c r="U23" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="V23" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W23" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X23" t="n">
         <v>5.4</v>
@@ -4552,37 +4619,37 @@
         <v>20.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AB23" t="n">
-        <v>92.90000000000001</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="AC23" t="n">
-        <v>-1.1</v>
+        <v>-0.3</v>
       </c>
       <c r="AD23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
         <v>20</v>
       </c>
       <c r="AF23" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AG23" t="n">
         <v>20</v>
       </c>
       <c r="AH23" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AI23" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ23" t="n">
         <v>21</v>
       </c>
       <c r="AK23" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AL23" t="n">
         <v>28</v>
@@ -4591,13 +4658,13 @@
         <v>28</v>
       </c>
       <c r="AN23" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AO23" t="n">
         <v>21</v>
       </c>
       <c r="AP23" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AQ23" t="n">
         <v>25</v>
@@ -4612,13 +4679,13 @@
         <v>14</v>
       </c>
       <c r="AU23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AW23" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AX23" t="n">
         <v>9</v>
@@ -4627,16 +4694,16 @@
         <v>10</v>
       </c>
       <c r="AZ23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA23" t="n">
         <v>22</v>
       </c>
       <c r="BB23" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="BC23" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -4665,70 +4732,70 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E24" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F24" t="n">
         <v>9</v>
       </c>
       <c r="G24" t="n">
-        <v>0.71</v>
+        <v>0.7</v>
       </c>
       <c r="H24" t="n">
         <v>48</v>
       </c>
       <c r="I24" t="n">
-        <v>42.1</v>
+        <v>42</v>
       </c>
       <c r="J24" t="n">
-        <v>85.5</v>
+        <v>85.09999999999999</v>
       </c>
       <c r="K24" t="n">
-        <v>0.492</v>
+        <v>0.493</v>
       </c>
       <c r="L24" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="M24" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="N24" t="n">
-        <v>0.37</v>
+        <v>0.368</v>
       </c>
       <c r="O24" t="n">
         <v>16.9</v>
       </c>
       <c r="P24" t="n">
-        <v>21.9</v>
+        <v>21.7</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.773</v>
+        <v>0.776</v>
       </c>
       <c r="R24" t="n">
-        <v>8.699999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="S24" t="n">
-        <v>32.5</v>
+        <v>32.6</v>
       </c>
       <c r="T24" t="n">
-        <v>41.1</v>
+        <v>40.9</v>
       </c>
       <c r="U24" t="n">
-        <v>28</v>
+        <v>27.9</v>
       </c>
       <c r="V24" t="n">
-        <v>13.5</v>
+        <v>13.7</v>
       </c>
       <c r="W24" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="X24" t="n">
         <v>6.8</v>
       </c>
       <c r="Y24" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Z24" t="n">
         <v>19</v>
@@ -4737,13 +4804,13 @@
         <v>19.7</v>
       </c>
       <c r="AB24" t="n">
-        <v>109.4</v>
+        <v>109.1</v>
       </c>
       <c r="AC24" t="n">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AD24" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>3</v>
@@ -4782,16 +4849,16 @@
         <v>26</v>
       </c>
       <c r="AQ24" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AR24" t="n">
         <v>30</v>
       </c>
       <c r="AS24" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="AT24" t="n">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AU24" t="n">
         <v>1</v>
@@ -4800,13 +4867,13 @@
         <v>6</v>
       </c>
       <c r="AW24" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AX24" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ24" t="n">
         <v>2</v>
@@ -4818,7 +4885,7 @@
         <v>1</v>
       </c>
       <c r="BC24" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -4847,16 +4914,16 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F25" t="n">
         <v>12</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6</v>
+        <v>0.586</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
@@ -4871,70 +4938,70 @@
         <v>0.463</v>
       </c>
       <c r="L25" t="n">
-        <v>6.4</v>
+        <v>6.3</v>
       </c>
       <c r="M25" t="n">
-        <v>16.7</v>
+        <v>16.6</v>
       </c>
       <c r="N25" t="n">
-        <v>0.382</v>
+        <v>0.38</v>
       </c>
       <c r="O25" t="n">
         <v>17.4</v>
       </c>
       <c r="P25" t="n">
-        <v>23.2</v>
+        <v>23.3</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.75</v>
+        <v>0.749</v>
       </c>
       <c r="R25" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S25" t="n">
         <v>29.5</v>
       </c>
       <c r="T25" t="n">
-        <v>39.7</v>
+        <v>39.8</v>
       </c>
       <c r="U25" t="n">
-        <v>21.8</v>
+        <v>21.7</v>
       </c>
       <c r="V25" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W25" t="n">
         <v>5.7</v>
       </c>
       <c r="X25" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Y25" t="n">
         <v>3.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>19.6</v>
+        <v>19.8</v>
       </c>
       <c r="AA25" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="AB25" t="n">
         <v>95.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.3</v>
+        <v>-0.6</v>
       </c>
       <c r="AD25" t="n">
+        <v>15</v>
+      </c>
+      <c r="AE25" t="n">
         <v>10</v>
       </c>
-      <c r="AE25" t="n">
-        <v>9</v>
-      </c>
       <c r="AF25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AG25" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH25" t="n">
         <v>20</v>
@@ -4943,13 +5010,13 @@
         <v>18</v>
       </c>
       <c r="AJ25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK25" t="n">
         <v>8</v>
       </c>
       <c r="AL25" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AM25" t="n">
         <v>20</v>
@@ -4967,16 +5034,16 @@
         <v>18</v>
       </c>
       <c r="AR25" t="n">
+        <v>23</v>
+      </c>
+      <c r="AS25" t="n">
         <v>24</v>
-      </c>
-      <c r="AS25" t="n">
-        <v>23</v>
       </c>
       <c r="AT25" t="n">
         <v>27</v>
       </c>
       <c r="AU25" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AV25" t="n">
         <v>9</v>
@@ -4985,7 +5052,7 @@
         <v>29</v>
       </c>
       <c r="AX25" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY25" t="n">
         <v>1</v>
@@ -5000,7 +5067,7 @@
         <v>19</v>
       </c>
       <c r="BC25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -5029,67 +5096,67 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E26" t="n">
         <v>11</v>
       </c>
       <c r="F26" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>0.379</v>
+        <v>0.393</v>
       </c>
       <c r="H26" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>35.1</v>
+        <v>35</v>
       </c>
       <c r="J26" t="n">
-        <v>78.5</v>
+        <v>78.2</v>
       </c>
       <c r="K26" t="n">
         <v>0.448</v>
       </c>
       <c r="L26" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="M26" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="N26" t="n">
-        <v>0.351</v>
+        <v>0.358</v>
       </c>
       <c r="O26" t="n">
-        <v>21.3</v>
+        <v>21.4</v>
       </c>
       <c r="P26" t="n">
         <v>27.1</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.789</v>
+        <v>0.787</v>
       </c>
       <c r="R26" t="n">
-        <v>10.3</v>
+        <v>10.2</v>
       </c>
       <c r="S26" t="n">
-        <v>28.7</v>
+        <v>28.6</v>
       </c>
       <c r="T26" t="n">
-        <v>39</v>
+        <v>38.8</v>
       </c>
       <c r="U26" t="n">
         <v>17.7</v>
       </c>
       <c r="V26" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="W26" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="X26" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="Y26" t="n">
         <v>5.8</v>
@@ -5098,25 +5165,25 @@
         <v>22.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>23.2</v>
+        <v>23.4</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.40000000000001</v>
+        <v>97.3</v>
       </c>
       <c r="AC26" t="n">
-        <v>-3.7</v>
+        <v>-3.3</v>
       </c>
       <c r="AD26" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE26" t="n">
         <v>21</v>
       </c>
       <c r="AF26" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AG26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH26" t="n">
         <v>8</v>
@@ -5137,19 +5204,19 @@
         <v>21</v>
       </c>
       <c r="AN26" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="AO26" t="n">
         <v>7</v>
       </c>
       <c r="AP26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ26" t="n">
         <v>4</v>
       </c>
       <c r="AR26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS26" t="n">
         <v>29</v>
@@ -5161,10 +5228,10 @@
         <v>29</v>
       </c>
       <c r="AV26" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AX26" t="n">
         <v>28</v>
@@ -5173,10 +5240,10 @@
         <v>25</v>
       </c>
       <c r="AZ26" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA26" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BB26" t="n">
         <v>15</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -5211,28 +5278,28 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E27" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F27" t="n">
         <v>8</v>
       </c>
       <c r="G27" t="n">
-        <v>0.724</v>
+        <v>0.714</v>
       </c>
       <c r="H27" t="n">
         <v>48</v>
       </c>
       <c r="I27" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J27" t="n">
         <v>79.59999999999999</v>
       </c>
       <c r="K27" t="n">
-        <v>0.466</v>
+        <v>0.464</v>
       </c>
       <c r="L27" t="n">
         <v>8.199999999999999</v>
@@ -5241,58 +5308,58 @@
         <v>21.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.39</v>
+        <v>0.387</v>
       </c>
       <c r="O27" t="n">
-        <v>16.6</v>
+        <v>16.4</v>
       </c>
       <c r="P27" t="n">
-        <v>21.8</v>
+        <v>21.6</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.762</v>
+        <v>0.76</v>
       </c>
       <c r="R27" t="n">
         <v>10.1</v>
       </c>
       <c r="S27" t="n">
-        <v>31.8</v>
+        <v>31.7</v>
       </c>
       <c r="T27" t="n">
-        <v>41.9</v>
+        <v>41.8</v>
       </c>
       <c r="U27" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="V27" t="n">
         <v>12.8</v>
       </c>
       <c r="W27" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="X27" t="n">
         <v>3.8</v>
       </c>
       <c r="Y27" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z27" t="n">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="AA27" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.90000000000001</v>
+        <v>98.5</v>
       </c>
       <c r="AC27" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="AE27" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AF27" t="n">
         <v>3</v>
@@ -5304,13 +5371,13 @@
         <v>24</v>
       </c>
       <c r="AI27" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="AJ27" t="n">
         <v>20</v>
       </c>
       <c r="AK27" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AL27" t="n">
         <v>4</v>
@@ -5328,7 +5395,7 @@
         <v>27</v>
       </c>
       <c r="AQ27" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="AR27" t="n">
         <v>25</v>
@@ -5337,22 +5404,22 @@
         <v>10</v>
       </c>
       <c r="AT27" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AU27" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AV27" t="n">
         <v>3</v>
       </c>
       <c r="AW27" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY27" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ27" t="n">
         <v>1</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -5471,25 +5538,25 @@
         <v>-6.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AE28" t="n">
         <v>25</v>
       </c>
       <c r="AF28" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AG28" t="n">
         <v>26</v>
       </c>
       <c r="AH28" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AI28" t="n">
         <v>7</v>
       </c>
       <c r="AJ28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AK28" t="n">
         <v>23</v>
@@ -5501,25 +5568,25 @@
         <v>26</v>
       </c>
       <c r="AN28" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO28" t="n">
         <v>16</v>
       </c>
       <c r="AP28" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AQ28" t="n">
         <v>10</v>
       </c>
       <c r="AR28" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS28" t="n">
         <v>3</v>
       </c>
       <c r="AT28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU28" t="n">
         <v>17</v>
@@ -5537,7 +5604,7 @@
         <v>20</v>
       </c>
       <c r="AZ28" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA28" t="n">
         <v>20</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -5668,7 +5735,7 @@
         <v>21</v>
       </c>
       <c r="AI29" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ29" t="n">
         <v>8</v>
@@ -5701,7 +5768,7 @@
         <v>16</v>
       </c>
       <c r="AT29" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AU29" t="n">
         <v>11</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -5853,7 +5920,7 @@
         <v>3</v>
       </c>
       <c r="AJ30" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AK30" t="n">
         <v>2</v>
@@ -5883,7 +5950,7 @@
         <v>28</v>
       </c>
       <c r="AT30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AU30" t="n">
         <v>2</v>
@@ -5892,7 +5959,7 @@
         <v>20</v>
       </c>
       <c r="AW30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX30" t="n">
         <v>24</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>1.8</v>
       </c>
       <c r="AD31" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6029,7 +6096,7 @@
         <v>13</v>
       </c>
       <c r="AH31" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AI31" t="n">
         <v>8</v>
@@ -6050,10 +6117,10 @@
         <v>16</v>
       </c>
       <c r="AO31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP31" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ31" t="n">
         <v>5</v>
@@ -6062,7 +6129,7 @@
         <v>9</v>
       </c>
       <c r="AS31" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT31" t="n">
         <v>6</v>
@@ -6092,7 +6159,7 @@
         <v>11</v>
       </c>
       <c r="BC31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BD31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-30-2007-08</t>
+          <t>2007-12-30</t>
         </is>
       </c>
     </row>
